--- a/AAII_Financials/Yearly/DOCN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DOCN_YR_FIN.xlsx
@@ -3809,7 +3809,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-129100</v>
+        <v>-255900</v>
       </c>
       <c r="E91" s="3">
         <v>-178200</v>
